--- a/selenium-tests/StainScope_Android_Appium_Test_Report.xlsx
+++ b/selenium-tests/StainScope_Android_Appium_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="112">
   <si>
     <t>📱 StainScope Android Appium &amp; Native E2E Test Report</t>
   </si>
@@ -74,7 +74,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-21T09:23:00.668Z</t>
+    <t>2026-08-21T09:28:01.646Z</t>
   </si>
   <si>
     <t>AND-TC002</t>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Navigated to Welcome screen</t>
-  </si>
-  <si>
-    <t>2026-08-21T09:23:00.669Z</t>
   </si>
   <si>
     <t>AND-TC003</t>
@@ -938,423 +935,423 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
       <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>36</v>
       </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
       <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
       <c r="G6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
       <c r="G7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>51</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>52</v>
       </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
       <c r="G8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>56</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
       <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>60</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>61</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>62</v>
       </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
       <c r="G10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>67</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
         <v>70</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>71</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>73</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>74</v>
       </c>
-      <c r="F12" t="s">
-        <v>75</v>
-      </c>
       <c r="G12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="F13" t="s">
-        <v>79</v>
-      </c>
       <c r="G13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>83</v>
       </c>
-      <c r="F14" t="s">
-        <v>84</v>
-      </c>
       <c r="G14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>86</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>89</v>
       </c>
-      <c r="F15" t="s">
-        <v>90</v>
-      </c>
       <c r="G15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>92</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>95</v>
       </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
       <c r="G16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
         <v>97</v>
       </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>98</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>99</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>100</v>
       </c>
-      <c r="F17" t="s">
-        <v>101</v>
-      </c>
       <c r="G17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
         <v>102</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>103</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>104</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>105</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s">
-        <v>107</v>
-      </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
         <v>108</v>
       </c>
-      <c r="B19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>109</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>110</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>111</v>
       </c>
-      <c r="F19" t="s">
-        <v>112</v>
-      </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
